--- a/uploads/Planilha_Online_LUCIANEQUARTO.xlsx
+++ b/uploads/Planilha_Online_LUCIANEQUARTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Helton Cardoso\CADASTRO PRODUTO\LUCIANE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CD3251-B47B-4CA9-AC3E-BEFCB998E740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE17683-0B4E-43A1-BCB9-B9053CA665CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E3533EE-8A81-4A60-93EF-A94A643EAA99}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E3533EE-8A81-4A60-93EF-A94A643EAA99}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7349" uniqueCount="1614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7469" uniqueCount="1618">
   <si>
     <t>EAN</t>
   </si>
@@ -10927,12 +10927,6 @@
   </si>
   <si>
     <t>Branco/Grey</t>
-  </si>
-  <si>
-    <t>Freijo</t>
-  </si>
-  <si>
-    <t>Freijo/Mocca</t>
   </si>
   <si>
     <t>&lt;b&gt;Guarda Roupa Queen Modulado CP01 Delphi Avelã L01           - Mpozenato&lt;/b&gt;&lt;br&gt;&lt;/br&gt;
@@ -17705,6 +17699,9 @@
   </si>
   <si>
     <t>Freijó/Mocca</t>
+  </si>
+  <si>
+    <t>Branco</t>
   </si>
 </sst>
 </file>
@@ -19753,7 +19750,7 @@
         <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>253</v>
@@ -20217,7 +20214,7 @@
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>278</v>
@@ -20681,7 +20678,7 @@
         <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>303</v>
@@ -21609,7 +21606,7 @@
         <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>354</v>
@@ -22073,7 +22070,7 @@
         <v>78</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>383</v>
@@ -23001,7 +22998,7 @@
         <v>78</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>434</v>
@@ -23465,7 +23462,7 @@
         <v>78</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>434</v>
@@ -24161,7 +24158,7 @@
         <v>78</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>499</v>
@@ -25089,7 +25086,7 @@
         <v>78</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>549</v>
@@ -26945,7 +26942,7 @@
         <v>78</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>499</v>
@@ -27873,7 +27870,7 @@
         <v>78</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>698</v>
@@ -28801,7 +28798,7 @@
         <v>78</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>752</v>
@@ -29729,7 +29726,7 @@
         <v>78</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>805</v>
@@ -30193,7 +30190,7 @@
         <v>78</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>0</v>
+        <v>1506</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>832</v>
@@ -31308,7 +31305,7 @@
         <v>78</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>898</v>
@@ -31409,7 +31406,7 @@
         <v>78</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>904</v>
@@ -31510,7 +31507,7 @@
         <v>78</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>910</v>
@@ -31727,7 +31724,7 @@
         <v>78</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>925</v>
@@ -31843,7 +31840,7 @@
         <v>78</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>931</v>
@@ -31959,7 +31956,7 @@
         <v>78</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>710</v>
@@ -32075,7 +32072,7 @@
         <v>78</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>944</v>
@@ -32191,7 +32188,7 @@
         <v>78</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>952</v>
@@ -32307,7 +32304,7 @@
         <v>78</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>960</v>
@@ -32423,7 +32420,7 @@
         <v>78</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>967</v>
@@ -32539,7 +32536,7 @@
         <v>78</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>975</v>
@@ -32655,7 +32652,7 @@
         <v>78</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>983</v>
@@ -32828,7 +32825,7 @@
         <v>79</v>
       </c>
       <c r="AC128" s="6" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="AD128" s="5" t="s">
         <v>174</v>
@@ -32945,7 +32942,7 @@
         <v>79</v>
       </c>
       <c r="AC129" s="6" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="AD129" s="5" t="s">
         <v>174</v>
@@ -33062,7 +33059,7 @@
         <v>79</v>
       </c>
       <c r="AC130" s="6" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="AD130" s="5" t="s">
         <v>174</v>
@@ -33179,7 +33176,7 @@
         <v>79</v>
       </c>
       <c r="AC131" s="6" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="AD131" s="5" t="s">
         <v>174</v>
@@ -33296,7 +33293,7 @@
         <v>79</v>
       </c>
       <c r="AC132" s="6" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="AD132" s="5" t="s">
         <v>174</v>
@@ -33413,7 +33410,7 @@
         <v>79</v>
       </c>
       <c r="AC133" s="6" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="AD133" s="5" t="s">
         <v>174</v>
@@ -33530,7 +33527,7 @@
         <v>79</v>
       </c>
       <c r="AC134" s="6" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="AD134" s="5" t="s">
         <v>174</v>
@@ -33647,7 +33644,7 @@
         <v>79</v>
       </c>
       <c r="AC135" s="6" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="AD135" s="5" t="s">
         <v>174</v>
@@ -33764,7 +33761,7 @@
         <v>79</v>
       </c>
       <c r="AC136" s="6" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="AD136" s="5" t="s">
         <v>174</v>
@@ -33881,7 +33878,7 @@
         <v>79</v>
       </c>
       <c r="AC137" s="6" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="AD137" s="5" t="s">
         <v>174</v>
@@ -33998,7 +33995,7 @@
         <v>79</v>
       </c>
       <c r="AC138" s="6" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="AD138" s="5" t="s">
         <v>174</v>
@@ -34115,7 +34112,7 @@
         <v>79</v>
       </c>
       <c r="AC139" s="6" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="AD139" s="5" t="s">
         <v>174</v>
@@ -34232,7 +34229,7 @@
         <v>79</v>
       </c>
       <c r="AC140" s="6" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="AD140" s="5" t="s">
         <v>174</v>
@@ -34349,7 +34346,7 @@
         <v>79</v>
       </c>
       <c r="AC141" s="6" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="AD141" s="5" t="s">
         <v>174</v>
@@ -34466,7 +34463,7 @@
         <v>79</v>
       </c>
       <c r="AC142" s="6" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="AD142" s="5" t="s">
         <v>174</v>
@@ -34583,7 +34580,7 @@
         <v>79</v>
       </c>
       <c r="AC143" s="6" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="AD143" s="5" t="s">
         <v>174</v>
@@ -34700,7 +34697,7 @@
         <v>79</v>
       </c>
       <c r="AC144" s="6" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="AD144" s="5" t="s">
         <v>174</v>
@@ -34817,7 +34814,7 @@
         <v>79</v>
       </c>
       <c r="AC145" s="6" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="AD145" s="5" t="s">
         <v>174</v>
@@ -34934,7 +34931,7 @@
         <v>79</v>
       </c>
       <c r="AC146" s="6" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="AD146" s="5" t="s">
         <v>174</v>
@@ -35051,7 +35048,7 @@
         <v>79</v>
       </c>
       <c r="AC147" s="6" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="AD147" s="5" t="s">
         <v>174</v>
@@ -35168,7 +35165,7 @@
         <v>79</v>
       </c>
       <c r="AC148" s="6" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="AD148" s="5" t="s">
         <v>174</v>
@@ -35285,7 +35282,7 @@
         <v>79</v>
       </c>
       <c r="AC149" s="6" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="AD149" s="5" t="s">
         <v>174</v>
@@ -35402,7 +35399,7 @@
         <v>79</v>
       </c>
       <c r="AC150" s="6" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="AD150" s="5" t="s">
         <v>174</v>
@@ -35519,7 +35516,7 @@
         <v>79</v>
       </c>
       <c r="AC151" s="6" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="AD151" s="5" t="s">
         <v>174</v>
@@ -35636,7 +35633,7 @@
         <v>79</v>
       </c>
       <c r="AC152" s="6" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="AD152" s="5" t="s">
         <v>174</v>
@@ -35752,7 +35749,7 @@
         <v>79</v>
       </c>
       <c r="AC153" s="3" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="AD153" s="2" t="s">
         <v>174</v>
@@ -35868,7 +35865,7 @@
         <v>79</v>
       </c>
       <c r="AC154" s="3" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="AD154" s="2" t="s">
         <v>174</v>
@@ -35984,7 +35981,7 @@
         <v>79</v>
       </c>
       <c r="AC155" s="3" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="AD155" s="2" t="s">
         <v>174</v>
@@ -36100,7 +36097,7 @@
         <v>79</v>
       </c>
       <c r="AC156" s="3" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="AD156" s="2" t="s">
         <v>174</v>
@@ -36216,7 +36213,7 @@
         <v>79</v>
       </c>
       <c r="AC157" s="3" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="AD157" s="2" t="s">
         <v>174</v>
@@ -36332,7 +36329,7 @@
         <v>79</v>
       </c>
       <c r="AC158" s="3" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="AD158" s="2" t="s">
         <v>174</v>
@@ -36448,7 +36445,7 @@
         <v>79</v>
       </c>
       <c r="AC159" s="3" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="AD159" s="2" t="s">
         <v>174</v>
@@ -36564,7 +36561,7 @@
         <v>79</v>
       </c>
       <c r="AC160" s="3" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="AD160" s="2" t="s">
         <v>174</v>
@@ -36680,7 +36677,7 @@
         <v>79</v>
       </c>
       <c r="AC161" s="3" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="AD161" s="2" t="s">
         <v>174</v>
@@ -36796,7 +36793,7 @@
         <v>79</v>
       </c>
       <c r="AC162" s="3" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="AD162" s="2" t="s">
         <v>174</v>
@@ -36912,7 +36909,7 @@
         <v>79</v>
       </c>
       <c r="AC163" s="3" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="AD163" s="2" t="s">
         <v>174</v>
@@ -37028,7 +37025,7 @@
         <v>79</v>
       </c>
       <c r="AC164" s="3" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="AD164" s="2" t="s">
         <v>174</v>
@@ -37144,7 +37141,7 @@
         <v>79</v>
       </c>
       <c r="AC165" s="3" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="AD165" s="2" t="s">
         <v>174</v>
@@ -37260,7 +37257,7 @@
         <v>79</v>
       </c>
       <c r="AC166" s="3" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="AD166" s="2" t="s">
         <v>174</v>
@@ -37376,7 +37373,7 @@
         <v>79</v>
       </c>
       <c r="AC167" s="3" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="AD167" s="2" t="s">
         <v>174</v>
@@ -37492,7 +37489,7 @@
         <v>79</v>
       </c>
       <c r="AC168" s="3" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="AD168" s="2" t="s">
         <v>174</v>
@@ -37608,7 +37605,7 @@
         <v>79</v>
       </c>
       <c r="AC169" s="3" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="AD169" s="2" t="s">
         <v>174</v>
@@ -37724,7 +37721,7 @@
         <v>79</v>
       </c>
       <c r="AC170" s="3" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="AD170" s="2" t="s">
         <v>174</v>
@@ -37840,7 +37837,7 @@
         <v>79</v>
       </c>
       <c r="AC171" s="3" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="AD171" s="2" t="s">
         <v>174</v>
@@ -37956,7 +37953,7 @@
         <v>79</v>
       </c>
       <c r="AC172" s="3" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="AD172" s="2" t="s">
         <v>174</v>
@@ -38072,7 +38069,7 @@
         <v>79</v>
       </c>
       <c r="AC173" s="3" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="AD173" s="2" t="s">
         <v>174</v>
@@ -38188,7 +38185,7 @@
         <v>79</v>
       </c>
       <c r="AC174" s="3" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="AD174" s="2" t="s">
         <v>174</v>
@@ -38304,7 +38301,7 @@
         <v>79</v>
       </c>
       <c r="AC175" s="3" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="AD175" s="2" t="s">
         <v>174</v>
@@ -38420,7 +38417,7 @@
         <v>79</v>
       </c>
       <c r="AC176" s="3" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="AD176" s="2" t="s">
         <v>174</v>
@@ -38536,7 +38533,7 @@
         <v>79</v>
       </c>
       <c r="AC177" s="3" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="AD177" s="2" t="s">
         <v>174</v>
@@ -38652,7 +38649,7 @@
         <v>79</v>
       </c>
       <c r="AC178" s="3" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="AD178" s="2" t="s">
         <v>174</v>
@@ -38768,7 +38765,7 @@
         <v>79</v>
       </c>
       <c r="AC179" s="3" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="AD179" s="2" t="s">
         <v>174</v>
@@ -38884,7 +38881,7 @@
         <v>79</v>
       </c>
       <c r="AC180" s="3" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="AD180" s="2" t="s">
         <v>174</v>
@@ -39000,7 +38997,7 @@
         <v>79</v>
       </c>
       <c r="AC181" s="3" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="AD181" s="2" t="s">
         <v>174</v>
@@ -39116,7 +39113,7 @@
         <v>79</v>
       </c>
       <c r="AC182" s="3" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="AD182" s="2" t="s">
         <v>174</v>
@@ -39232,7 +39229,7 @@
         <v>79</v>
       </c>
       <c r="AC183" s="3" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="AD183" s="2" t="s">
         <v>174</v>
@@ -39348,7 +39345,7 @@
         <v>79</v>
       </c>
       <c r="AC184" s="3" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="AD184" s="2" t="s">
         <v>174</v>
@@ -39464,7 +39461,7 @@
         <v>79</v>
       </c>
       <c r="AC185" s="3" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="AD185" s="2" t="s">
         <v>174</v>
@@ -39580,7 +39577,7 @@
         <v>79</v>
       </c>
       <c r="AC186" s="3" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="AD186" s="2" t="s">
         <v>174</v>
@@ -39696,7 +39693,7 @@
         <v>79</v>
       </c>
       <c r="AC187" s="3" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="AD187" s="2" t="s">
         <v>174</v>
@@ -39812,7 +39809,7 @@
         <v>79</v>
       </c>
       <c r="AC188" s="3" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="AD188" s="2" t="s">
         <v>174</v>
@@ -39928,7 +39925,7 @@
         <v>79</v>
       </c>
       <c r="AC189" s="3" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="AD189" s="2" t="s">
         <v>174</v>
@@ -40044,7 +40041,7 @@
         <v>79</v>
       </c>
       <c r="AC190" s="3" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="AD190" s="2" t="s">
         <v>174</v>
@@ -40160,7 +40157,7 @@
         <v>79</v>
       </c>
       <c r="AC191" s="3" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="AD191" s="2" t="s">
         <v>174</v>
@@ -40276,7 +40273,7 @@
         <v>79</v>
       </c>
       <c r="AC192" s="3" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="AD192" s="2" t="s">
         <v>174</v>
@@ -40392,7 +40389,7 @@
         <v>79</v>
       </c>
       <c r="AC193" s="3" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="AD193" s="2" t="s">
         <v>174</v>
@@ -40508,7 +40505,7 @@
         <v>79</v>
       </c>
       <c r="AC194" s="3" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="AD194" s="2" t="s">
         <v>174</v>
@@ -40624,7 +40621,7 @@
         <v>79</v>
       </c>
       <c r="AC195" s="3" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="AD195" s="2" t="s">
         <v>174</v>
@@ -40740,7 +40737,7 @@
         <v>79</v>
       </c>
       <c r="AC196" s="3" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="AD196" s="2" t="s">
         <v>174</v>
@@ -40856,7 +40853,7 @@
         <v>79</v>
       </c>
       <c r="AC197" s="3" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="AD197" s="2" t="s">
         <v>174</v>
@@ -40912,7 +40909,7 @@
         <v>78</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="I198" s="2" t="s">
         <v>1354</v>
@@ -40972,7 +40969,7 @@
         <v>79</v>
       </c>
       <c r="AC198" s="3" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="AD198" s="2" t="s">
         <v>174</v>
@@ -41088,7 +41085,7 @@
         <v>79</v>
       </c>
       <c r="AC199" s="3" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="AD199" s="2" t="s">
         <v>174</v>
@@ -41204,7 +41201,7 @@
         <v>79</v>
       </c>
       <c r="AC200" s="3" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="AD200" s="2" t="s">
         <v>174</v>
@@ -41320,7 +41317,7 @@
         <v>79</v>
       </c>
       <c r="AC201" s="3" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="AD201" s="2" t="s">
         <v>174</v>
@@ -41436,7 +41433,7 @@
         <v>79</v>
       </c>
       <c r="AC202" s="3" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="AD202" s="2" t="s">
         <v>174</v>
@@ -41552,7 +41549,7 @@
         <v>79</v>
       </c>
       <c r="AC203" s="3" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="AD203" s="2" t="s">
         <v>174</v>
@@ -41668,7 +41665,7 @@
         <v>79</v>
       </c>
       <c r="AC204" s="3" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="AD204" s="2" t="s">
         <v>174</v>
@@ -41784,7 +41781,7 @@
         <v>79</v>
       </c>
       <c r="AC205" s="3" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="AD205" s="2" t="s">
         <v>174</v>
@@ -41900,7 +41897,7 @@
         <v>79</v>
       </c>
       <c r="AC206" s="3" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="AD206" s="2" t="s">
         <v>174</v>
@@ -42016,7 +42013,7 @@
         <v>79</v>
       </c>
       <c r="AC207" s="3" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="AD207" s="2" t="s">
         <v>174</v>
@@ -42132,7 +42129,7 @@
         <v>79</v>
       </c>
       <c r="AC208" s="3" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="AD208" s="2" t="s">
         <v>174</v>
@@ -42248,7 +42245,7 @@
         <v>79</v>
       </c>
       <c r="AC209" s="3" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="AD209" s="2" t="s">
         <v>174</v>
@@ -42364,7 +42361,7 @@
         <v>79</v>
       </c>
       <c r="AC210" s="3" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="AD210" s="2" t="s">
         <v>174</v>
@@ -42480,7 +42477,7 @@
         <v>79</v>
       </c>
       <c r="AC211" s="3" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="AD211" s="2" t="s">
         <v>174</v>
@@ -42596,7 +42593,7 @@
         <v>79</v>
       </c>
       <c r="AC212" s="3" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="AD212" s="2" t="s">
         <v>174</v>
@@ -42712,7 +42709,7 @@
         <v>79</v>
       </c>
       <c r="AC213" s="3" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="AD213" s="2" t="s">
         <v>174</v>
@@ -42828,7 +42825,7 @@
         <v>79</v>
       </c>
       <c r="AC214" s="3" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="AD214" s="2" t="s">
         <v>174</v>
@@ -42944,7 +42941,7 @@
         <v>79</v>
       </c>
       <c r="AC215" s="3" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="AD215" s="2" t="s">
         <v>174</v>
@@ -43060,7 +43057,7 @@
         <v>79</v>
       </c>
       <c r="AC216" s="3" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="AD216" s="2" t="s">
         <v>174</v>
@@ -43176,7 +43173,7 @@
         <v>79</v>
       </c>
       <c r="AC217" s="3" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="AD217" s="2" t="s">
         <v>174</v>
@@ -43292,7 +43289,7 @@
         <v>79</v>
       </c>
       <c r="AC218" s="3" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="AD218" s="2" t="s">
         <v>174</v>
@@ -43408,7 +43405,7 @@
         <v>79</v>
       </c>
       <c r="AC219" s="3" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="AD219" s="2" t="s">
         <v>174</v>
@@ -43524,7 +43521,7 @@
         <v>79</v>
       </c>
       <c r="AC220" s="3" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="AD220" s="2" t="s">
         <v>174</v>
@@ -43640,7 +43637,7 @@
         <v>79</v>
       </c>
       <c r="AC221" s="3" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="AD221" s="2" t="s">
         <v>174</v>
@@ -43756,7 +43753,7 @@
         <v>79</v>
       </c>
       <c r="AC222" s="3" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="AD222" s="2" t="s">
         <v>174</v>
@@ -43872,7 +43869,7 @@
         <v>79</v>
       </c>
       <c r="AC223" s="3" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="AD223" s="2" t="s">
         <v>174</v>
@@ -43988,7 +43985,7 @@
         <v>79</v>
       </c>
       <c r="AC224" s="3" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="AD224" s="2" t="s">
         <v>174</v>
@@ -44104,7 +44101,7 @@
         <v>79</v>
       </c>
       <c r="AC225" s="3" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="AD225" s="2" t="s">
         <v>174</v>
@@ -44220,7 +44217,7 @@
         <v>79</v>
       </c>
       <c r="AC226" s="3" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="AD226" s="2" t="s">
         <v>174</v>
@@ -44336,7 +44333,7 @@
         <v>79</v>
       </c>
       <c r="AC227" s="3" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="AD227" s="2" t="s">
         <v>174</v>
